--- a/Monaco_Besoins_IT_v4.xlsx
+++ b/Monaco_Besoins_IT_v4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rberger-my.sharepoint.com/personal/theo_thivard_rolandberger_com/Documents/Desktop/TMT/Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{F6B55F70-8E07-48DB-B0EA-E687927205DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65BF1007-0474-49FC-BA01-F40CBA5406DF}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{F6B55F70-8E07-48DB-B0EA-E687927205DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5040891F-AF64-495E-B13D-80A6BAA8884D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6538,7 +6538,7 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>0.74581390430837979</c:v>
+                  <c:v>7.5629922912243943</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.12100312257300898</c:v>
@@ -6556,7 +6556,7 @@
                   <c:v>0.21051316577768281</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.6843442384062171</c:v>
+                  <c:v>8.5015226253222291</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6639,7 +6639,7 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>0.80892941382919248</c:v>
+                  <c:v>8.1479165167807555</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.16226360014168051</c:v>
@@ -6657,7 +6657,7 @@
                   <c:v>0.61185584239846225</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.6332046318596247</c:v>
+                  <c:v>9.9721917348111866</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6740,7 +6740,7 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>0.97357331083025023</c:v>
+                  <c:v>9.7264937088458758</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.24020857327627559</c:v>
@@ -6758,7 +6758,7 @@
                   <c:v>1.6428936026152947</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.9751398631546691</c:v>
+                  <c:v>13.728060261170295</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7750,7 +7750,7 @@
         <v>10</v>
       </c>
       <c r="F9" s="9">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>11</v>
@@ -8830,7 +8830,7 @@
         <v>66</v>
       </c>
       <c r="F57" s="12">
-        <v>2000</v>
+        <v>2000000</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>67</v>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="F59" s="13">
         <f>F57+9*F58</f>
-        <v>2450</v>
+        <v>2000450</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>72</v>
@@ -9993,11 +9993,11 @@
       </c>
       <c r="F9" s="53">
         <f>'1_Inputs&amp;Hyp'!F9</f>
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="G9" s="14">
         <f>F9-H9</f>
-        <v>61.16</v>
+        <v>781.16</v>
       </c>
       <c r="H9" s="14">
         <f>F21*G21/1000</f>
@@ -10178,11 +10178,11 @@
       </c>
       <c r="F17" s="14">
         <f>SUM(F9:F16)</f>
-        <v>2800.3199999999997</v>
+        <v>3520.3199999999997</v>
       </c>
       <c r="G17" s="14">
         <f t="shared" ref="G17:H17" si="0">SUM(G9:G16)</f>
-        <v>141.16</v>
+        <v>861.16</v>
       </c>
       <c r="H17" s="14">
         <f t="shared" si="0"/>
@@ -11181,7 +11181,7 @@
       </c>
       <c r="E59" s="8">
         <f>F$9</f>
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="F59" s="15">
         <f>(1+_xlfn.XLOOKUP($D$56,$F$33:$H$33,$F$34:$H$34))^9</f>
@@ -11193,11 +11193,11 @@
       </c>
       <c r="H59" s="23">
         <f>('1_Inputs&amp;Hyp'!F59/'1_Inputs&amp;Hyp'!F57)*'1_Inputs&amp;Hyp'!F62</f>
-        <v>11.67578125</v>
+        <v>9.5333945312499999</v>
       </c>
       <c r="I59" s="8">
         <f>H$9*F59*G59+G$9*H59</f>
-        <v>736.60632524284426</v>
+        <v>7469.6220160240937</v>
       </c>
       <c r="J59" s="15">
         <f>_xlfn.XLOOKUP($D$56,$F$33:$H$33,$F$40:$H$40)</f>
@@ -11205,11 +11205,11 @@
       </c>
       <c r="K59" s="8">
         <f t="shared" ref="K59:K66" si="1">I59*J59</f>
-        <v>36.830316262142212</v>
+        <v>373.48110080120472</v>
       </c>
       <c r="L59" s="8">
         <f>I59+K59</f>
-        <v>773.43664150498648</v>
+        <v>7843.1031168252985</v>
       </c>
       <c r="M59" s="15">
         <f t="shared" ref="M59:M64" si="2">_xlfn.XLOOKUP($D$56,$F$33:$H$33,$F$46:$H$46)</f>
@@ -11221,15 +11221,15 @@
       </c>
       <c r="O59" s="8">
         <f>I59*M59+K59*N59</f>
-        <v>745.81390430837985</v>
+        <v>7562.9922912243946</v>
       </c>
       <c r="P59" s="4">
         <f>O59/1000</f>
-        <v>0.74581390430837979</v>
+        <v>7.5629922912243943</v>
       </c>
       <c r="R59" s="71">
         <f>O59</f>
-        <v>745.81390430837985</v>
+        <v>7562.9922912243946</v>
       </c>
     </row>
     <row r="60" spans="2:18">
@@ -11640,33 +11640,33 @@
       </c>
       <c r="E68" s="16">
         <f>SUM(E59:E66)</f>
-        <v>2800.3199999999997</v>
+        <v>3520.3199999999997</v>
       </c>
       <c r="F68" s="16"/>
       <c r="G68" s="16"/>
       <c r="H68" s="16"/>
       <c r="I68" s="16">
         <f>SUM(I59:I66)</f>
-        <v>4082.2460937035084</v>
+        <v>10815.261784484757</v>
       </c>
       <c r="J68" s="16"/>
       <c r="K68" s="16">
         <f>SUM(K59:K66)</f>
-        <v>243.43294935305354</v>
+        <v>580.08373389211602</v>
       </c>
       <c r="L68" s="16">
         <f>SUM(L59:L66)</f>
-        <v>4325.6790430565616</v>
+        <v>11395.345518376875</v>
       </c>
       <c r="M68" s="16"/>
       <c r="N68" s="16"/>
       <c r="O68" s="16">
         <f>SUM(O59:O66)</f>
-        <v>1684.3442384062171</v>
+        <v>8501.5226253222299</v>
       </c>
       <c r="P68" s="16">
         <f>SUM(P59:P66)</f>
-        <v>1.6843442384062171</v>
+        <v>8.5015226253222309</v>
       </c>
     </row>
     <row r="69" spans="3:18">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="E74" s="8">
         <f>F$9</f>
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="F74" s="15">
         <f>(1+_xlfn.XLOOKUP($D$71,$F$33:$H$33,$F$34:$H$34))^9</f>
@@ -11793,11 +11793,11 @@
       </c>
       <c r="H74" s="30">
         <f>('1_Inputs&amp;Hyp'!F59/'1_Inputs&amp;Hyp'!F57)*'1_Inputs&amp;Hyp'!F62</f>
-        <v>11.67578125</v>
+        <v>9.5333945312499999</v>
       </c>
       <c r="I74" s="8">
         <f>H$9*F74*G74+G$9*H74</f>
-        <v>742.13707690751608</v>
+        <v>7475.1527676887663</v>
       </c>
       <c r="J74" s="15">
         <f>_xlfn.XLOOKUP($D$71,$F$33:$H$33,$F$40:$H$40)</f>
@@ -11805,11 +11805,11 @@
       </c>
       <c r="K74" s="8">
         <f t="shared" ref="K74:K81" si="7">I74*J74</f>
-        <v>111.32056153612741</v>
+        <v>1121.2729151533149</v>
       </c>
       <c r="L74" s="8">
         <f>I74+K74</f>
-        <v>853.45763844364353</v>
+        <v>8596.4256828420803</v>
       </c>
       <c r="M74" s="15">
         <f t="shared" ref="M74:M79" si="8">_xlfn.XLOOKUP($D$71,$F$33:$H$33,$F$46:$H$46)</f>
@@ -11821,15 +11821,15 @@
       </c>
       <c r="O74" s="8">
         <f>I74*M74+K74*N74</f>
-        <v>808.92941382919253</v>
+        <v>8147.916516780755</v>
       </c>
       <c r="P74" s="4">
         <f>O74/1000</f>
-        <v>0.80892941382919248</v>
+        <v>8.1479165167807555</v>
       </c>
       <c r="R74" s="71">
         <f>O74</f>
-        <v>808.92941382919253</v>
+        <v>8147.916516780755</v>
       </c>
     </row>
     <row r="75" spans="3:18">
@@ -12238,33 +12238,33 @@
       </c>
       <c r="E83" s="16">
         <f>SUM(E74:E81)</f>
-        <v>2800.3199999999997</v>
+        <v>3520.3199999999997</v>
       </c>
       <c r="F83" s="16"/>
       <c r="G83" s="16"/>
       <c r="H83" s="16"/>
       <c r="I83" s="16">
         <f>SUM(I74:I81)</f>
-        <v>4942.0038483228855</v>
+        <v>11675.019539104136</v>
       </c>
       <c r="J83" s="16"/>
       <c r="K83" s="16">
         <f>SUM(K74:K81)</f>
-        <v>839.0949465787694</v>
+        <v>1849.0473001959567</v>
       </c>
       <c r="L83" s="16">
         <f>SUM(L74:L81)</f>
-        <v>5781.0987949016544</v>
+        <v>13524.066839300089</v>
       </c>
       <c r="M83" s="16"/>
       <c r="N83" s="16"/>
       <c r="O83" s="16">
         <f>SUM(O74:O81)</f>
-        <v>2633.2046318596249</v>
+        <v>9972.1917348111856</v>
       </c>
       <c r="P83" s="16">
         <f>SUM(P74:P81)</f>
-        <v>2.6332046318596247</v>
+        <v>9.9721917348111866</v>
       </c>
     </row>
     <row r="84" spans="3:18">
@@ -12379,7 +12379,7 @@
       </c>
       <c r="E89" s="8">
         <f>F$9</f>
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="F89" s="15">
         <f>(1+_xlfn.XLOOKUP($D$86,$F$33:$H$33,$F$34:$H$34))^9</f>
@@ -12391,11 +12391,11 @@
       </c>
       <c r="H89" s="30">
         <f>('1_Inputs&amp;Hyp'!F59/'1_Inputs&amp;Hyp'!F57)*'1_Inputs&amp;Hyp'!F62</f>
-        <v>11.67578125</v>
+        <v>9.5333945312499999</v>
       </c>
       <c r="I89" s="8">
         <f>H$9*F89*G89+G$9*H89</f>
-        <v>748.90254679250017</v>
+        <v>7481.91823757375</v>
       </c>
       <c r="J89" s="15">
         <f>_xlfn.XLOOKUP($D$86,$F$33:$H$33,$F$40:$H$40)</f>
@@ -12403,11 +12403,11 @@
       </c>
       <c r="K89" s="8">
         <f t="shared" ref="K89:K96" si="13">I89*J89</f>
-        <v>224.67076403775005</v>
+        <v>2244.575471272125</v>
       </c>
       <c r="L89" s="8">
         <f>I89+K89</f>
-        <v>973.57331083025019</v>
+        <v>9726.4937088458755</v>
       </c>
       <c r="M89" s="15">
         <f t="shared" ref="M89:M94" si="14">_xlfn.XLOOKUP($D$86,$F$33:$H$33,$F$46:$H$46)</f>
@@ -12419,15 +12419,15 @@
       </c>
       <c r="O89" s="8">
         <f>I89*M89+K89*N89</f>
-        <v>973.57331083025019</v>
+        <v>9726.4937088458755</v>
       </c>
       <c r="P89" s="4">
         <f>O89/1000</f>
-        <v>0.97357331083025023</v>
+        <v>9.7264937088458758</v>
       </c>
       <c r="R89" s="71">
         <f>O89</f>
-        <v>973.57331083025019</v>
+        <v>9726.4937088458755</v>
       </c>
     </row>
     <row r="90" spans="3:18">
@@ -12836,33 +12836,33 @@
       </c>
       <c r="E98" s="16">
         <f>SUM(E89:E96)</f>
-        <v>2800.3199999999997</v>
+        <v>3520.3199999999997</v>
       </c>
       <c r="F98" s="16"/>
       <c r="G98" s="16"/>
       <c r="H98" s="16"/>
       <c r="I98" s="16">
         <f>SUM(I89:I96)</f>
-        <v>6138.5637488335606</v>
+        <v>12871.579439614809</v>
       </c>
       <c r="J98" s="16"/>
       <c r="K98" s="16">
         <f>SUM(K89:K96)</f>
-        <v>2023.3521073771435</v>
+        <v>4043.2568146115191</v>
       </c>
       <c r="L98" s="16">
         <f>SUM(L89:L96)</f>
-        <v>8161.9158562107041</v>
+        <v>16914.836254226328</v>
       </c>
       <c r="M98" s="16"/>
       <c r="N98" s="16"/>
       <c r="O98" s="16">
         <f>SUM(O89:O96)</f>
-        <v>4975.139863154669</v>
+        <v>13728.060261170293</v>
       </c>
       <c r="P98" s="16">
         <f>SUM(P89:P96)</f>
-        <v>4.9751398631546691</v>
+        <v>13.728060261170295</v>
       </c>
     </row>
     <row r="99" spans="4:16">
@@ -13346,15 +13346,15 @@
       </c>
       <c r="C8" s="4">
         <f>'2_Calculs'!$F$17/10^3</f>
-        <v>2.8003199999999997</v>
+        <v>3.5203199999999999</v>
       </c>
       <c r="D8" s="4">
         <f>'2_Calculs'!$F$17/10^3</f>
-        <v>2.8003199999999997</v>
+        <v>3.5203199999999999</v>
       </c>
       <c r="E8" s="4">
         <f>'2_Calculs'!$F$17/10^3</f>
-        <v>2.8003199999999997</v>
+        <v>3.5203199999999999</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -13372,15 +13372,15 @@
       </c>
       <c r="C9" s="4">
         <f>'2_Calculs'!L68/10^3</f>
-        <v>4.3256790430565619</v>
+        <v>11.395345518376875</v>
       </c>
       <c r="D9" s="4">
         <f>'2_Calculs'!L83/10^3</f>
-        <v>5.7810987949016548</v>
+        <v>13.524066839300088</v>
       </c>
       <c r="E9" s="4">
         <f>'2_Calculs'!L98/10^3</f>
-        <v>8.1619158562107046</v>
+        <v>16.914836254226326</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -13398,15 +13398,15 @@
       </c>
       <c r="C10" s="35">
         <f>'2_Calculs'!P68</f>
-        <v>1.6843442384062171</v>
+        <v>8.5015226253222309</v>
       </c>
       <c r="D10" s="35">
         <f>'2_Calculs'!P83</f>
-        <v>2.6332046318596247</v>
+        <v>9.9721917348111866</v>
       </c>
       <c r="E10" s="35">
         <f>'2_Calculs'!P98</f>
-        <v>4.9751398631546691</v>
+        <v>13.728060261170295</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -13439,15 +13439,15 @@
       </c>
       <c r="C12" s="34">
         <f>C10/C9</f>
-        <v>0.38938261984782974</v>
+        <v>0.74605220277104567</v>
       </c>
       <c r="D12" s="34">
         <f t="shared" ref="D12:E12" si="0">D10/D9</f>
-        <v>0.45548514655757921</v>
+        <v>0.73736634499857867</v>
       </c>
       <c r="E12" s="34">
         <f t="shared" si="0"/>
-        <v>0.6095553973849045</v>
+        <v>0.8115987677823493</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -13465,15 +13465,15 @@
       </c>
       <c r="C13" s="33">
         <f>C9/C8</f>
-        <v>1.5447088343677018</v>
+        <v>3.2370197931940492</v>
       </c>
       <c r="D13" s="33">
         <f t="shared" ref="D13:E13" si="1">D9/D8</f>
-        <v>2.06444220478433</v>
+        <v>3.8417151961469664</v>
       </c>
       <c r="E13" s="33">
         <f t="shared" si="1"/>
-        <v>2.9146368472927042</v>
+        <v>4.8049143981871891</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
@@ -13576,15 +13576,15 @@
       </c>
       <c r="C19" s="4">
         <f>'2_Calculs'!P59</f>
-        <v>0.74581390430837979</v>
+        <v>7.5629922912243943</v>
       </c>
       <c r="D19" s="4">
         <f>'2_Calculs'!P74</f>
-        <v>0.80892941382919248</v>
+        <v>8.1479165167807555</v>
       </c>
       <c r="E19" s="4">
         <f>'2_Calculs'!P89</f>
-        <v>0.97357331083025023</v>
+        <v>9.7264937088458758</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
@@ -13732,15 +13732,15 @@
       </c>
       <c r="C25" s="6">
         <f>SUM(C19:C24)</f>
-        <v>1.6843442384062171</v>
+        <v>8.5015226253222291</v>
       </c>
       <c r="D25" s="6">
         <f>SUM(D19:D24)</f>
-        <v>2.6332046318596247</v>
+        <v>9.9721917348111866</v>
       </c>
       <c r="E25" s="6">
         <f>SUM(E19:E24)</f>
-        <v>4.9751398631546691</v>
+        <v>13.728060261170295</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -14841,6 +14841,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TranslatedLang xmlns="c8e751d2-3d37-4167-80fa-a7ac4017bdce" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E67A066FCD1E3F438488297A6C42CAF9" ma:contentTypeVersion="4" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="18f0f9b597039d9e780f83a3fa476528">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c8e751d2-3d37-4167-80fa-a7ac4017bdce" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a27a98dd884412d2ea335885e9b91a1f" ns2:_="">
     <xsd:import namespace="c8e751d2-3d37-4167-80fa-a7ac4017bdce"/>
@@ -14984,24 +15001,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4344C341-AD09-48CF-A9D3-1481B5BEA8A2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c8e751d2-3d37-4167-80fa-a7ac4017bdce"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TranslatedLang xmlns="c8e751d2-3d37-4167-80fa-a7ac4017bdce" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5EFFB68-C21E-4BD7-B2CB-20E039E408F5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7245038-B243-488C-BE74-9359FD82AB6C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -15017,22 +15035,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5EFFB68-C21E-4BD7-B2CB-20E039E408F5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4344C341-AD09-48CF-A9D3-1481B5BEA8A2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c8e751d2-3d37-4167-80fa-a7ac4017bdce"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>